--- a/tame_output/ON/bt/strategyON_20240908.xlsx
+++ b/tame_output/ON/bt/strategyON_20240908.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>52.3%</t>
+          <t>52.5%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2076</v>
+        <v>2077</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,7 +628,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>34.4%</t>
+          <t>35.2%</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>102.2%</t>
+          <t>102.0%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2076</v>
+        <v>2077</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>86.1%</t>
+          <t>85.8%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>137.8%</t>
+          <t>137.2%</t>
         </is>
       </c>
     </row>
@@ -921,7 +921,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.1%</t>
+          <t>108.0%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -931,11 +931,11 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.1%</t>
+          <t>52.0%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2076</v>
+        <v>2077</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.2%</t>
+          <t>21.8%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-48.9%</t>
+          <t>-47.3%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.6%</t>
+          <t>89.5%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>422.2%</t>
+          <t>422.3%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-660.9%</t>
+          <t>-661.6%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>31.1%</t>
+          <t>30.8%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1089,11 +1089,11 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.2%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2076</v>
+        <v>2077</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>13.1%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>27.2%</t>
+          <t>27.0%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-126.6%</t>
+          <t>-127.5%</t>
         </is>
       </c>
     </row>
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2076</v>
+        <v>2077</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>588.2%</t>
+          <t>588.4%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>102.7%</t>
+          <t>102.4%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2076</v>
+        <v>2077</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>94.0%</t>
+          <t>93.7%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>46.5%</t>
+          <t>45.9%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2079"/>
+  <dimension ref="A1:G2080"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -49362,7 +49362,7 @@
         <v>45541</v>
       </c>
       <c r="B2079" t="n">
-        <v>3.624724018933301</v>
+        <v>3.623960959762286</v>
       </c>
       <c r="C2079" t="n">
         <v>4.493831566905334</v>
@@ -49378,6 +49378,29 @@
       </c>
       <c r="G2079" t="n">
         <v>4.924866134961625</v>
+      </c>
+    </row>
+    <row r="2080">
+      <c r="A2080" s="2" t="n">
+        <v>45542</v>
+      </c>
+      <c r="B2080" t="n">
+        <v>3.633213467988017</v>
+      </c>
+      <c r="C2080" t="n">
+        <v>4.488063552849688</v>
+      </c>
+      <c r="D2080" t="n">
+        <v>-5.000307545192285</v>
+      </c>
+      <c r="E2080" t="n">
+        <v>2.487584110459027</v>
+      </c>
+      <c r="F2080" t="n">
+        <v>0.7183909467604842</v>
+      </c>
+      <c r="G2080" t="n">
+        <v>4.919098120905979</v>
       </c>
     </row>
   </sheetData>
